--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488156_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488156_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9665</v>
+        <v>4.5916</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3834</v>
+        <v>3.6979</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5831</v>
+        <v>0.8937</v>
       </c>
       <c r="G2" t="n">
         <v>4.3816</v>
@@ -610,13 +610,13 @@
         <v>1.1117</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0113</v>
+        <v>0.6364</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1737</v>
+        <v>1.4882</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1625</v>
+        <v>-0.8519</v>
       </c>
       <c r="V2" t="n">
         <v>0.3148</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.175</v>
+        <v>3.5673</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8412</v>
+        <v>3.135</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3338</v>
+        <v>0.4323</v>
       </c>
       <c r="G3" t="n">
         <v>3.0514</v>
@@ -688,13 +688,13 @@
         <v>0.1853</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2502</v>
+        <v>0.1421</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1094</v>
+        <v>0.1844</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1408</v>
+        <v>-0.0423</v>
       </c>
       <c r="V3" t="n">
         <v>0.1886</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8157</v>
+        <v>2.6697</v>
       </c>
       <c r="E4" t="n">
-        <v>2.964</v>
+        <v>2.6702</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1482</v>
+        <v>-0.0005</v>
       </c>
       <c r="G4" t="n">
         <v>0.9043</v>
@@ -766,13 +766,13 @@
         <v>1.4823</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0109</v>
+        <v>-0.157</v>
       </c>
       <c r="T4" t="n">
-        <v>2.0643</v>
+        <v>1.7705</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.0752</v>
+        <v>-1.9275</v>
       </c>
       <c r="V4" t="n">
         <v>0.4401</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PINA GUISADO</t>
+          <t>I. GARCIA REYES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0862</v>
+        <v>1.7481</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1743</v>
+        <v>2.0784</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0881</v>
+        <v>-0.3303</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1163</v>
+        <v>1.145</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4311</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3148</v>
+        <v>0.5589</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0051</v>
+        <v>-0.6263</v>
       </c>
       <c r="K5" t="n">
-        <v>0.575</v>
+        <v>-1.976</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5699</v>
+        <v>1.3497</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1112</v>
+        <v>1.7713</v>
       </c>
       <c r="N5" t="n">
-        <v>0.856</v>
+        <v>2.5622</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7448</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8529</v>
+        <v>1.1117</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3972</v>
+        <v>-0.194</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4661</v>
+        <v>2.7047</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.8633</v>
+        <v>-2.8987</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4407</v>
+        <v>-0.3147</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1888</v>
+        <v>-0.3147</v>
       </c>
     </row>
     <row r="6">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. GARCIA REYES</t>
+          <t>J. PINA GUISADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6692</v>
+        <v>0.8663</v>
       </c>
       <c r="E7" t="n">
-        <v>1.295</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6258</v>
+        <v>-0.0142</v>
       </c>
       <c r="G7" t="n">
-        <v>1.145</v>
+        <v>0.1163</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5862000000000001</v>
+        <v>1.4311</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5589</v>
+        <v>-1.3148</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6263</v>
+        <v>0.0051</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.976</v>
+        <v>0.575</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3497</v>
+        <v>-0.5699</v>
       </c>
       <c r="M7" t="n">
-        <v>1.7713</v>
+        <v>0.1112</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5622</v>
+        <v>0.856</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.7448</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1117</v>
+        <v>0.9264</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1117</v>
+        <v>1.8529</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2729</v>
+        <v>-0.6171</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9213</v>
+        <v>1.1724</v>
       </c>
       <c r="U7" t="n">
-        <v>-3.1942</v>
+        <v>-1.7895</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3147</v>
+        <v>0.4407</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3147</v>
+        <v>-0.1888</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
+          <t>D. CASTRO DIANEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3836</v>
+        <v>0.4544</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3375</v>
+        <v>1.3995</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.9539</v>
+        <v>-0.945</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1916</v>
+        <v>-0.8524</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.21</v>
+        <v>3.2503</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0185</v>
+        <v>-4.1028</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9014</v>
+        <v>-0.2358</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.8049</v>
+        <v>2.2927</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7063</v>
+        <v>-2.5285</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.093</v>
+        <v>-0.6167</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5949</v>
+        <v>0.9576</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.6878</v>
+        <v>-1.5743</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6676</v>
+        <v>1.297</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1117</v>
+        <v>2.2234</v>
       </c>
       <c r="S8" t="n">
-        <v>3.8716</v>
+        <v>-0.3044</v>
       </c>
       <c r="T8" t="n">
-        <v>4.6422</v>
+        <v>1.9328</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7705</v>
+        <v>-2.2372</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6289</v>
+        <v>0.3142</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5733</v>
+        <v>0.6289</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.2022</v>
+        <v>-0.3147</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. ESCAMILLA DE SANTOS</t>
+          <t>M. TRILLO MANGANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2964</v>
+        <v>0.0788</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2917</v>
+        <v>1.9581</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.9953</v>
+        <v>-1.8793</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7667</v>
+        <v>0.6367</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1455</v>
+        <v>0.2142</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9122</v>
+        <v>0.4225</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0655</v>
+        <v>0.9489</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8582</v>
+        <v>-0.5026</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2074</v>
+        <v>1.4515</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8322</v>
+        <v>-0.3123</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2873</v>
+        <v>0.7167</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.1196</v>
+        <v>-1.029</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7411</v>
+        <v>0.1853</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7411</v>
+        <v>0.1853</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7623</v>
+        <v>-0.1138</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5967</v>
+        <v>1.0091</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8344</v>
+        <v>-1.1229</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4403</v>
+        <v>-0.6294</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0697</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. CASTRO DIANEZ</t>
+          <t>D. ESCAMILLA DE SANTOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.428</v>
+        <v>-0.0953</v>
       </c>
       <c r="E10" t="n">
-        <v>0.714</v>
+        <v>2.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.142</v>
+        <v>-2.9953</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8524</v>
+        <v>-0.7667</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2503</v>
+        <v>1.1455</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.1028</v>
+        <v>-1.9122</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2358</v>
+        <v>1.0655</v>
       </c>
       <c r="K10" t="n">
-        <v>2.2927</v>
+        <v>0.8582</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.5285</v>
+        <v>0.2074</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6167</v>
+        <v>-1.8322</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9576</v>
+        <v>0.2873</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5743</v>
+        <v>-2.1196</v>
       </c>
       <c r="P10" t="n">
-        <v>1.297</v>
+        <v>0.7411</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2234</v>
+        <v>0.7411</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1868</v>
+        <v>0.3706</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2473</v>
+        <v>1.205</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.4341</v>
+        <v>-0.8344</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3142</v>
+        <v>-0.4403</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6289</v>
+        <v>0.6294</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3147</v>
+        <v>-1.0697</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. TRILLO MANGANO</t>
+          <t>J. PONCE GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.637</v>
+        <v>-2.0252</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5871</v>
+        <v>-0.8576</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.224</v>
+        <v>-1.1676</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6367</v>
+        <v>-1.693</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2142</v>
+        <v>0.2623</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4225</v>
+        <v>-1.9553</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9489</v>
+        <v>0.4234</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5026</v>
+        <v>0.2362</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4515</v>
+        <v>0.1872</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3123</v>
+        <v>-2.1164</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7167</v>
+        <v>0.0262</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.029</v>
+        <v>-2.1426</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1853</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8295</v>
+        <v>0.0945</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3619</v>
+        <v>0.2574</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4676</v>
+        <v>-0.1629</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6294</v>
+        <v>0.3144</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. PONCE GONZALEZ</t>
+          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6609</v>
+        <v>-2.1888</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.641</v>
+        <v>2.0852</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0199</v>
+        <v>-4.274</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.693</v>
+        <v>-1.1916</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2623</v>
+        <v>-1.21</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9553</v>
+        <v>0.0185</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4234</v>
+        <v>0.9014</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2362</v>
+        <v>-1.8049</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1872</v>
+        <v>2.7063</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1164</v>
+        <v>-2.093</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0262</v>
+        <v>0.5949</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.1426</v>
+        <v>-2.6878</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7411</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R12" t="n">
         <v>1.1117</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5412</v>
+        <v>1.2992</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.526</v>
+        <v>2.3898</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0152</v>
+        <v>-1.0906</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3144</v>
+        <v>-0.6289</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3144</v>
+        <v>1.5733</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.2022</v>
       </c>
     </row>
     <row r="13">
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.6108</v>
+        <v>10.611</v>
       </c>
       <c r="E13" t="n">
         <v>20.8913</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.2803</v>
+        <v>-10.2802</v>
       </c>
       <c r="G13" t="n">
-        <v>6.675700000000001</v>
+        <v>6.6757</v>
       </c>
       <c r="H13" t="n">
         <v>10.1701</v>
@@ -1444,13 +1444,13 @@
         <v>7.563700000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7682999999999999</v>
+        <v>0.7683000000000004</v>
       </c>
       <c r="L13" t="n">
         <v>6.7957</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8883000000000003</v>
+        <v>-0.8883000000000005</v>
       </c>
       <c r="N13" t="n">
         <v>9.401699999999998</v>
@@ -1459,7 +1459,7 @@
         <v>-10.2899</v>
       </c>
       <c r="P13" t="n">
-        <v>2.7793</v>
+        <v>2.779299999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-8.337900000000001</v>
@@ -1474,10 +1474,10 @@
         <v>14.1143</v>
       </c>
       <c r="U13" t="n">
-        <v>-12.9578</v>
+        <v>-12.9579</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.0004999999999997784</v>
+        <v>-0.000500000000000056</v>
       </c>
       <c r="W13" t="n">
         <v>7.5508</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0233</v>
+        <v>5.4247</v>
       </c>
       <c r="E14" t="n">
-        <v>6.8164</v>
+        <v>8.481199999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.7931</v>
+        <v>-3.0565</v>
       </c>
       <c r="G14" t="n">
         <v>5.2573</v>
@@ -1546,13 +1546,13 @@
         <v>1.297</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5311</v>
+        <v>-0.1296</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8207</v>
+        <v>0.8441</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7103</v>
+        <v>-0.9737</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6294</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3872</v>
+        <v>1.5742</v>
       </c>
       <c r="E15" t="n">
-        <v>7.3366</v>
+        <v>5.7698</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.9494</v>
+        <v>-4.1956</v>
       </c>
       <c r="G15" t="n">
         <v>1.9515</v>
@@ -1624,13 +1624,13 @@
         <v>1.1117</v>
       </c>
       <c r="S15" t="n">
-        <v>2.548</v>
+        <v>0.7349</v>
       </c>
       <c r="T15" t="n">
-        <v>3.9682</v>
+        <v>2.4013</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.4201</v>
+        <v>-1.6664</v>
       </c>
       <c r="V15" t="n">
         <v>-0.0005</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ARCONES DURAND</t>
+          <t>R. SANAHUJA TRESERRAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3908</v>
+        <v>-0.0669</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4781</v>
+        <v>1.0576</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.8689</v>
+        <v>-1.1245</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.3122</v>
+        <v>-0.587</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.4413</v>
+        <v>-0.2889</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8709</v>
+        <v>-0.2981</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.6638</v>
+        <v>0.5064</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.3902</v>
+        <v>0.2362</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7264</v>
+        <v>0.2702</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6484</v>
+        <v>-1.0934</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9489</v>
+        <v>-0.5251</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.5973</v>
+        <v>-0.5683</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.3706</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9276</v>
+        <v>-0.0358</v>
       </c>
       <c r="T16" t="n">
-        <v>6.1419</v>
+        <v>0.9218</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.2143</v>
+        <v>-0.9575</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2526</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.2526</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ELIAS GALLEGOS</t>
+          <t>R. MERINO LUQUE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7438</v>
+        <v>-1.1161</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4162</v>
+        <v>-0.2691</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3276</v>
+        <v>-0.847</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1532</v>
+        <v>-0.0801</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1072</v>
+        <v>-0.5548</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.046</v>
+        <v>0.4747</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.2843</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.2843</v>
+        <v>-0.6099</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.3271</v>
       </c>
       <c r="M17" t="n">
-        <v>0.131</v>
+        <v>-0.7973</v>
       </c>
       <c r="N17" t="n">
-        <v>0.177</v>
+        <v>0.0552</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.046</v>
+        <v>-0.8524</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4723</v>
+        <v>0.1318</v>
       </c>
       <c r="T17" t="n">
-        <v>0.868</v>
+        <v>0.5521</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3957</v>
+        <v>-0.4203</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.0629</v>
+        <v>0.3144</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.0629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. SECK DIOP</t>
+          <t>P. VILLAREJO CALATAYUD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2247</v>
+        <v>-1.2193</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.139</v>
+        <v>-0.331</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0856</v>
+        <v>-0.8883</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2462</v>
+        <v>1.9821</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6487</v>
+        <v>1.2036</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5974</v>
+        <v>0.7785</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.0245</v>
+        <v>3.2291</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.496</v>
+        <v>2.5121</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5284</v>
+        <v>0.7169</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7783</v>
+        <v>-1.247</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8473000000000001</v>
+        <v>-1.3085</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.0616</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5558999999999999</v>
+        <v>-2.7793</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-4.0763</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.297</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5285</v>
+        <v>-0.6737</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6266</v>
+        <v>0.2018</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0981</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="V18" t="n">
+        <v>0.2516</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="X18" t="n">
         <v>-0.0629</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.2589</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-1.3217</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. MERINO LUQUE</t>
+          <t>A. ELIAS GALLEGOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6138</v>
+        <v>-1.454</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-1.1018</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.953</v>
+        <v>-0.3522</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0801</v>
+        <v>-1.1532</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5548</v>
+        <v>-1.1072</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4747</v>
+        <v>-0.046</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7171999999999999</v>
+        <v>-1.2843</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6099</v>
+        <v>-1.2843</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3271</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7973</v>
+        <v>0.131</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0552</v>
+        <v>0.177</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8524</v>
+        <v>-0.046</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.4823</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3658</v>
+        <v>-0.2378</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1604</v>
+        <v>0.1825</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5263</v>
+        <v>-0.4203</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3144</v>
+        <v>-0.0629</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.0629</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. SANAHUJA TRESERRAS</t>
+          <t>K. SECK DIOP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.659</v>
+        <v>-1.8878</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4113</v>
+        <v>-0.4328</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2476</v>
+        <v>-1.455</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.587</v>
+        <v>-2.2462</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2889</v>
+        <v>-1.6487</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2981</v>
+        <v>-0.5974</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5064</v>
+        <v>-3.0245</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2362</v>
+        <v>-2.496</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2702</v>
+        <v>-0.5284</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0934</v>
+        <v>0.7783</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5251</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5683</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="P20" t="n">
         <v>0.5558999999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.3706</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9264</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6278</v>
+        <v>-0.1346</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5471</v>
+        <v>1.3328</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0806</v>
+        <v>-1.4674</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.0629</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.3217</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. VILLAREJO CALATAYUD</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4689</v>
+        <v>-2.1632</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4082</v>
+        <v>-1.4282</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0607</v>
+        <v>-0.735</v>
       </c>
       <c r="G21" t="n">
-        <v>1.9821</v>
+        <v>-1.1532</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2036</v>
+        <v>-0.4544</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7785</v>
+        <v>-0.6989</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2291</v>
+        <v>-1.2843</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5121</v>
+        <v>-0.6314</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7169</v>
+        <v>-0.6529</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.247</v>
+        <v>0.131</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3085</v>
+        <v>0.177</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0616</v>
+        <v>-0.046</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.0763</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9233</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8754</v>
+        <v>-0.1439</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0478</v>
+        <v>-0.4887</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2516</v>
+        <v>-0.3773</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.0629</v>
+        <v>-0.3773</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>U. FRISCIA PEREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5555</v>
+        <v>-2.4176</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.722</v>
+        <v>-1.2591</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8335</v>
+        <v>-1.1585</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1532</v>
+        <v>-1.7483</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4544</v>
+        <v>-1.4473</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6989</v>
+        <v>-0.301</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2843</v>
+        <v>-1.1892</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6314</v>
+        <v>-1.8942</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6529</v>
+        <v>0.705</v>
       </c>
       <c r="M22" t="n">
-        <v>0.131</v>
+        <v>-0.5591</v>
       </c>
       <c r="N22" t="n">
-        <v>0.177</v>
+        <v>0.4469</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.046</v>
+        <v>-1.006</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0249</v>
+        <v>-0.1135</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4377</v>
+        <v>0.8565</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.97</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3773</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>U. FRISCIA PEREZ</t>
+          <t>A. ARCONES DURAND</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7692</v>
+        <v>-2.8294</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.357</v>
+        <v>-0.3619</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4122</v>
+        <v>-2.4675</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7483</v>
+        <v>-4.3122</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4473</v>
+        <v>-3.4413</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.301</v>
+        <v>-0.8709</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1892</v>
+        <v>-3.6638</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.8942</v>
+        <v>-4.3902</v>
       </c>
       <c r="L23" t="n">
-        <v>0.705</v>
+        <v>0.7264</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5591</v>
+        <v>-0.6484</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4469</v>
+        <v>0.9489</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.006</v>
+        <v>-1.5973</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4651</v>
+        <v>0.489</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7586000000000001</v>
+        <v>3.3019</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2236</v>
+        <v>-2.8129</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.2526</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.2526</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5957</v>
+        <v>-3.8026</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2361</v>
+        <v>0.1556</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.3597</v>
+        <v>-3.9583</v>
       </c>
       <c r="G24" t="n">
         <v>-4.5864</v>
@@ -2326,13 +2326,13 @@
         <v>1.6676</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6949</v>
+        <v>0.0982</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1153</v>
+        <v>2.507</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.8102</v>
+        <v>-2.4088</v>
       </c>
       <c r="V24" t="n">
         <v>0.315</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.6109</v>
+        <v>-9.958</v>
       </c>
       <c r="E25" t="n">
-        <v>10.2805</v>
+        <v>10.2803</v>
       </c>
       <c r="F25" t="n">
-        <v>-20.8913</v>
+        <v>-20.2384</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.6757</v>
+        <v>-6.675699999999999</v>
       </c>
       <c r="H25" t="n">
         <v>-10.17</v>
@@ -2377,7 +2377,7 @@
         <v>3.4942</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8880999999999997</v>
+        <v>0.8880999999999983</v>
       </c>
       <c r="K25" t="n">
         <v>-9.4017</v>
@@ -2389,7 +2389,7 @@
         <v>-7.563999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7682</v>
+        <v>-0.7681999999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-6.7956</v>
@@ -2404,13 +2404,13 @@
         <v>8.337899999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.156499999999999</v>
+        <v>-0.5037000000000003</v>
       </c>
       <c r="T25" t="n">
-        <v>12.9581</v>
+        <v>12.9579</v>
       </c>
       <c r="U25" t="n">
-        <v>-14.1142</v>
+        <v>-13.4615</v>
       </c>
       <c r="V25" t="n">
         <v>0.0006000000000000449</v>
